--- a/基本設計/20_メッセージと例外_基本設計書.xlsx
+++ b/基本設計/20_メッセージと例外_基本設計書.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Rfd1b315d45884369"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R08360f53591c45a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="31_メッセージ" sheetId="32" r:id="R9643c85c9e4c4a18"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="32_例外処理" sheetId="33" r:id="Rdb24a9be54ea4e39"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="31A_画面Message対応" sheetId="34" r:id="Re543441004d54908"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Re32277a1e45f46f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R359cdb237a934b0c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="31_メッセージ" sheetId="32" r:id="R07182570e3704da3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="32_例外処理" sheetId="33" r:id="R4da5dcfd81b6433c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="31A_画面Message対応" sheetId="34" r:id="R237e1ffa99db4f8d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1223,10 +1223,7 @@
       <x:c r="F16" s="170"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" t="str">
-        <x:v>本書は Company WorkHub の基本設計内容を定義する。
-Ver.1.8 は状態変更入口、API/DB制約、取込Transaction、日報一意制約、通知・Token保持を整合した再Review対応版である。</x:v>
-      </x:c>
+      <x:c r="A17"/>
       <x:c r="C17"/>
       <x:c r="D17"/>
       <x:c r="E17"/>
@@ -1241,25 +1238,22 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19"/>
-      <x:c r="B19" s="212" t="str">
-        <x:v>本書は Company WorkHub の基本設計内容を定義する。
-Ver.1.7 は状態変更入口、API/DB制約、取込Transaction、日報一意制約、通知・Token保持を整合した再Review対応版である。</x:v>
-      </x:c>
-      <x:c r="C19" s="212"/>
-      <x:c r="D19" s="212"/>
-      <x:c r="E19" s="212"/>
-      <x:c r="F19" s="212"/>
-      <x:c r="G19" s="212"/>
-      <x:c r="H19" s="212"/>
+      <x:c r="B19"/>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+      <x:c r="G19"/>
+      <x:c r="H19"/>
     </x:row>
     <x:row r="20">
-      <x:c r="B20" s="212"/>
-      <x:c r="C20" s="212"/>
-      <x:c r="D20" s="212"/>
-      <x:c r="E20" s="212"/>
-      <x:c r="F20" s="212"/>
-      <x:c r="G20" s="212"/>
-      <x:c r="H20" s="212"/>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+      <x:c r="G20"/>
+      <x:c r="H20"/>
     </x:row>
     <x:row r="21">
       <x:c r="B21" s="212"/>
